--- a/survey_templates/031_sync_settings_survey--survey_templates.xlsx
+++ b/survey_templates/031_sync_settings_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1150,8 +1150,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'performance'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Performance'}</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Security'}</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'usability'}</t>
+          <t>usability</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Usability'}</t>
+          <t>Usability</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
